--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
+          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Jr.Python Developer (Intern)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>p99soft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=76f42dbc27d37597</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
+          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle CX Solution Architect(Functional)</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Systems Engineer (Supply Chain)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, GCP, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0c167b0b4e8118</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Systems Engineer (Supply Chain)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>API Gateway, ECS, RDS, GCP, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0c167b0b4e8118</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af12bc7187e4862c</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tower semiconductor</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,42 +2981,497 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MAPDEVS CORP.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sonos</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ithaca, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Managing Engineer (US)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Mount Laurel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Data Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>ASSA ABLOY Group</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>New Haven, CT, US USA</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D86" t="n">
         <v>10.4</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tower semiconductor</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
+          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Murex</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
+          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jr.Python Developer (Intern)</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>p99soft</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f42dbc27d37597</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer - Murex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Jr.Python Developer (Intern)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>p99soft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=76f42dbc27d37597</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
+          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,77 +1746,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Advanced Medical Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a34608b53a9554</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Advanced Medical Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd297d26cd48490</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,15 +2088,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Systems Engineer (Supply Chain)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, GCP, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0c167b0b4e8118</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Systems Engineer (Supply Chain)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>API Gateway, ECS, RDS, GCP, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0c167b0b4e8118</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tower semiconductor</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,260 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>New Haven, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tower semiconductor</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jr.Python Developer (Intern)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>p99soft</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, IAM, RDS, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76f42dbc27d37597</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
@@ -2288,25 +2288,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Systems Engineer (Supply Chain)</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>API Gateway, ECS, RDS, GCP, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0c167b0b4e8118</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tower semiconductor</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3645,76 +3645,6 @@
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>ASSA ABLOY Group</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>New Haven, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Tower semiconductor</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Newport Beach, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3163,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tower semiconductor</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,50 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tower semiconductor</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
@@ -3023,25 +3023,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
@@ -3163,12 +3163,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
+          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,94 +1616,94 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Advanced Medical Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a34608b53a9554</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Advanced Medical Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd297d26cd48490</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Advanced Medical Management</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a34608b53a9554</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Advanced Medical Management</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd297d26cd48490</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
@@ -2988,25 +2988,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,69 +3286,69 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Tower semiconductor</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,50 +3636,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Tower semiconductor</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Newport Beach, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
         </is>
       </c>
     </row>
@@ -2743,12 +2743,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
@@ -3303,25 +3303,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
@@ -3513,17 +3513,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tower semiconductor</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,50 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tower semiconductor</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,24 +3041,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tower semiconductor</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,15 +3671,50 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tower semiconductor</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tower semiconductor</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,50 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tower semiconductor</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Advanced Medical Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a34608b53a9554</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a34608b53a9554</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd297d26cd48490</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Advanced Medical Management</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd297d26cd48490</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,29 +2551,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Tower semiconductor</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,50 +3706,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Tower semiconductor</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Newport Beach, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Architect - MySQL</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Azure, Databricks, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67ae1ade25d4115</t>
+          <t>https://www.indeed.com/viewjob?jk=62b7232e7951bd03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Spark</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b7232e7951bd03</t>
+          <t>https://www.indeed.com/viewjob?jk=dbdf2a1acd1d6f97</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Teleflex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, GCP, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd470eb429ea88c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Teleflex</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, GCP, Cloud Storage, Spark</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
+          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
+          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
         </is>
       </c>
     </row>
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
+          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Senior Software Engineer - Murex</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Murex</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
         </is>
       </c>
     </row>
@@ -1868,52 +1868,52 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Advanced Medical Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a34608b53a9554</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, Tableau, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,29 +2551,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Sr. Network Engineer- Versa SDWAN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Epic Willow Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Global Path Resources</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,24 +3076,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,42 +3356,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,102 +3436,102 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tower semiconductor</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,225 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>New Haven, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tower semiconductor</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Newport Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbdf2a1acd1d6f97</t>
+          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Teleflex</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, GCP, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
+          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
+          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
+          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Murex</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
+          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,69 +1851,69 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Advanced Medical Management</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Snowflake, SQL Server, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd297d26cd48490</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Western Camps, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,29 +2551,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Sr. Network Engineer- Versa SDWAN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer- Versa SDWAN</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Epic Willow Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Global Path Resources</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c686a51920df281d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,59 +2946,59 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Senior Systems Analyst, CRK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
@@ -3478,25 +3478,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,192 +3741,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Infrastructure Architect</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f14365db2087acc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Enterprise Data Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Full Stack AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Freedom Mortgage</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Marlton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>ASSA ABLOY Group</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>New Haven, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>CIM IT Application Engineer - Fab Automation &amp; MES</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Tower semiconductor</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Newport Beach, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Scala, Oracle, SQL Server, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c61a10ef209a4b5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,129 +1746,129 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,15 +1878,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Western Camps, Inc.</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer- Versa SDWAN</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Sr. Network Engineer- Versa SDWAN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,59 +2946,59 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Systems Analyst, CRK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85202d8fd6461588</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,94 +3401,94 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,29 +3601,29 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=09da89624990c354</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
+          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
         </is>
       </c>
     </row>
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,77 +626,77 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
@@ -1868,52 +1868,52 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,69 +1956,69 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer- Versa SDWAN</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Sr. Network Engineer- Versa SDWAN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,139 +3391,139 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,29 +3566,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,29 +3636,29 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09da89624990c354</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,157 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>New Haven, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PatientPoint</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
@@ -1343,25 +1343,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
+          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2057,46 +2057,46 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer- Versa SDWAN</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Network Engineer- Versa SDWAN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,59 +3086,59 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,104 +3496,104 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,29 +3741,29 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Enterprise Software Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer in Test</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PatientPoint</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,15 +3881,155 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>New Haven, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PatientPoint</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,42 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,42 +2106,42 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
@@ -2918,25 +2918,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,199 +2946,199 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,42 +3506,42 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
@@ -3553,47 +3553,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Enterprise Software Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,19 +3681,19 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer in Test</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>PatientPoint</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,260 +3776,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Enterprise Software Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Viventium Software</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Lantern</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>J2B GLOBAL LLC</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Full Stack AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Freedom Mortgage</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Marlton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>ASSA ABLOY Group</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>New Haven, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Software Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>PatientPoint</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior . Net Backend Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Spark</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b7232e7951bd03</t>
+          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,69 +1326,69 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1401,29 +1401,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kansas Judicial Branch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,94 +1896,94 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -2316,42 +2316,42 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=15ccdfb6af12e7c0</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,29 +2726,29 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer- Versa SDWAN</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Network Engineer- Versa SDWAN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2967,38 +2967,38 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=d54a3fd932b2489e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,42 +3506,42 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
@@ -3553,47 +3553,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Enterprise Software Architect</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer in Test</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PatientPoint</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,15 +3776,365 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Janus Henderson Investors</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Managing Engineer (US)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Mount Laurel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MuleSoft Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Enterprise Software Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Viventium Software</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - App Reliability</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - EMC Life</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EMC Insurance</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PatientPoint</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
+          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AWS DevOps Engineer</t>
+          <t>Infrastructure Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
+          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -2281,59 +2281,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=15ccdfb6af12e7c0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ccdfb6af12e7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stride, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Specialist - System Management</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>Sr. Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, RDS, Azure, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7216e95a38186a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Sr. Network Engineer- Versa SDWAN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer- Versa SDWAN</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54a3fd932b2489e</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,104 +3496,104 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Senior Managing Engineer (US)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Enterprise Software Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
+          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
+          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Enterprise Software Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Software Engineer in Test</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>PatientPoint</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4065,76 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>J2B GLOBAL LLC</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>PatientPoint</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
         </is>

--- a/results/job_matches_2026-08-11.xlsx
+++ b/results/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior . Net Backend Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Healthfirst</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7642aa199d34181</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Remote Snowflake Certified Architect / Senior Developer</t>
+          <t>Senior . Net Backend Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MindBoard</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
+          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
         </is>
       </c>
     </row>
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=528f5a1d87795372</t>
+          <t>https://www.indeed.com/viewjob?jk=dc07515a51a0557e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1687bf15e954aff7</t>
+          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,227 +1046,227 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32a773d465489919</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57f41d8722742e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffb9bdd4054a81</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60134942af123155</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6fc12bd1ac759b</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1cf60650add3267</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Infrastructure Data Analytics Engineer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338218edd2094f18</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
@@ -1278,42 +1278,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e1094bc8a8173</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Data &amp; Analytics Engineer - Office of Judicial Administration</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kansas Judicial Branch</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd55fb088f0f1a57</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Sequoia Connect</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e904a72543c1613d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rochester Hills, MI, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer III : AI/ML Solutions</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7109737319b6dd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer III : AI/ML Solutions</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f52f71a986160cea</t>
+          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c11f470fecf7abb</t>
+          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85aa006633a68b30</t>
+          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ccdfb6af12e7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Site Reliability Engineers</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Careers Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Analytics Engineer - US (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Luxury Presence</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba274c5ce462b944</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stride, Inc.</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e5377d70baf9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Sr. Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, SNS, API Gateway, RDS, Azure, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,102 +2491,102 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7216e95a38186a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Specialist - System Management</t>
+          <t>Business Intelligence Developer II / Web Analytics Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Dynamo Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, MySQL, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e86d021035a6db3</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineers</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Careers Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733a6bebc4ff1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer - US (Remote)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Luxury Presence</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4a77761da5e87d9</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,234 +2736,234 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16a74809c4dfda2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Quality Assurance Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, RDS, Azure, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7216e95a38186a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Oracle, ETL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f57100e67c19fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II / Web Analytics Developer</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dynamo Technologies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c998a72fff8ea1</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer- Versa SDWAN</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=908e3006d07b4364</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Software Engineer, Records</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Magna Legal Services</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,84 +3436,84 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Records</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Magna Legal Services</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd84a93f643ae447</t>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Enterprise Software Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b97ef9ad96dfc39</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Managing Engineer (US)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,297 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, Scala, ELT, DataOps, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8246143088401853</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Enterprise Software Architect</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Viventium Software</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Lantern</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45c7a33a5d7a2996</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - App Reliability</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - EMC Life</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>EMC Insurance</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>J2B GLOBAL LLC</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Software Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>PatientPoint</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
         </is>
       </c>
     </row>
